--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.50385415805081</v>
+        <v>2.519376300683257</v>
       </c>
       <c r="D2" t="n">
-        <v>15.10768069959132</v>
+        <v>2.45499811368359</v>
       </c>
       <c r="E2" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F2" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.389383571106181</v>
+        <v>1.200774830304754</v>
       </c>
       <c r="D3" t="n">
-        <v>12.66085809758234</v>
+        <v>2.05738944085713</v>
       </c>
       <c r="E3" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F3" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.67856757146533</v>
+        <v>6.447767230363116</v>
       </c>
       <c r="D4" t="n">
-        <v>40.52742052118048</v>
+        <v>6.585705834691828</v>
       </c>
       <c r="E4" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F4" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.07073367973682</v>
+        <v>4.398994222957233</v>
       </c>
       <c r="D5" t="n">
-        <v>27.93746797995309</v>
+        <v>4.539838546742377</v>
       </c>
       <c r="E5" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F5" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.985107923648757</v>
+        <v>1.622580037592923</v>
       </c>
       <c r="D6" t="n">
-        <v>25.08671090738687</v>
+        <v>4.076590522450367</v>
       </c>
       <c r="E6" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F6" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.12951546500395</v>
+        <v>2.621046263063143</v>
       </c>
       <c r="D7" t="n">
-        <v>27.16946934407088</v>
+        <v>4.415038768411518</v>
       </c>
       <c r="E7" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F7" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.2567843377532</v>
+        <v>3.454227454884895</v>
       </c>
       <c r="D8" t="n">
-        <v>20.48575012727646</v>
+        <v>3.328934395682426</v>
       </c>
       <c r="E8" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F8" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.58200923907206</v>
+        <v>3.01957650134921</v>
       </c>
       <c r="D9" t="n">
-        <v>18.56918475271262</v>
+        <v>3.017492522315801</v>
       </c>
       <c r="E9" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F9" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.64657356560516</v>
+        <v>5.955068204410838</v>
       </c>
       <c r="D10" t="n">
-        <v>36.63134826404693</v>
+        <v>5.952594092907626</v>
       </c>
       <c r="E10" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F10" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.5035184701759</v>
+        <v>5.606821751403584</v>
       </c>
       <c r="D11" t="n">
-        <v>34.36479381027195</v>
+        <v>5.584278994169192</v>
       </c>
       <c r="E11" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F11" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.36971882703093</v>
+        <v>3.472579309392527</v>
       </c>
       <c r="D12" t="n">
-        <v>21.12658965302706</v>
+        <v>3.433070818616898</v>
       </c>
       <c r="E12" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F12" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.77278914058222</v>
+        <v>4.025578235344611</v>
       </c>
       <c r="D13" t="n">
-        <v>24.98187796829252</v>
+        <v>4.059555169847535</v>
       </c>
       <c r="E13" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F13" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.4463530400129</v>
+        <v>7.060032369002097</v>
       </c>
       <c r="D14" t="n">
-        <v>43.69035001012485</v>
+        <v>7.099681876645287</v>
       </c>
       <c r="E14" t="n">
-        <v>10.93011365383676</v>
+        <v>1.776143468748474</v>
       </c>
       <c r="F14" t="n">
-        <v>9.247485391367986</v>
+        <v>1.502716376097298</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
